--- a/InputData/elec/TCAMRB/Trans Cap Across Modeled Region Border.xlsx
+++ b/InputData/elec/TCAMRB/Trans Cap Across Modeled Region Border.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10211"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\World Resources Institute\TRAC City - HK 2050 is now\eps-1.4.3-hk-wipB\eps-1.4.3-hk-wipB\InputData\elec\TCAMRB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lawrenceiu/Desktop/eps-us-3.4.7 working_D0227_T1543_woking/eps-us-3.4.7 HK working/InputData/elec/TCAMRB/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_8E7830F4C9C179ECF804EF4553438ED3C4B6935C" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{08DA311F-B553-41D8-A12E-0939F696A0B2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E5A7BB-0C30-4A43-B495-3D0566476B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="9345" yWindow="1035" windowWidth="10455" windowHeight="10695" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,10 +18,18 @@
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -29,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="49">
   <si>
     <t>TCAMRB Transmission Capacity Across Modeled Region Border</t>
   </si>
@@ -39,6 +47,9 @@
   <si>
     <t>News from China Electricity Concil (in Chinese)</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>China Electricity Concil(CEC)</t>
   </si>
   <si>
     <t>1）南方电网与香港电力20年合作共赢之路(20 years of win-win cooperation between China Southern power grid and HongKong power)</t>
@@ -104,7 +115,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="新細明體"/>
         <family val="3"/>
         <charset val="134"/>
         <scheme val="minor"/>
@@ -207,18 +218,36 @@
     <t>MW</t>
   </si>
   <si>
-    <t>China Electricity Concil(CEC)</t>
+    <t>https://cec.org.cn/detail/index.html?3-318329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTE: the article mentions that the maximum transmission capacity between Hong Kong and Guangdong was 1.8million kW and that during the duration of the 14FYP, they play to increase the amount to 2.7 million kW. As of 12/23, unsure what the progress is </t>
+  </si>
+  <si>
+    <t>Note, in 2023 Hong Kong govt decide to build almost same capacity of cross boundary receive station as current</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> https://www.info.gov.hk/gia/general/202303/15/P2023031500378.htm</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>current is 1800, in the 2024 model update we assume it will become 3600</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -226,13 +255,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -241,7 +270,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -249,7 +278,7 @@
     <font>
       <sz val="7"/>
       <color rgb="FF292727"/>
-      <name val="Calibri"/>
+      <name val="新細明體"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -259,6 +288,21 @@
       <color rgb="FF333333"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -284,10 +328,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -298,9 +344,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="3">
+    <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="千分位" xfId="1" builtinId="3"/>
+    <cellStyle name="超連結" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -315,147 +368,10 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>551883</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="图片 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="863600" y="4464050"/>
-          <a:ext cx="5384233" cy="825500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>541461</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>146050</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="图片 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1028700" y="6623050"/>
-          <a:ext cx="5354761" cy="635000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>234950</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>82550</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>165586</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="图片 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1225550" y="7842250"/>
-          <a:ext cx="5245100" cy="438636"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -493,9 +409,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -528,26 +444,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -580,26 +479,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -773,19 +655,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B53"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="14.140625" customWidth="1"/>
-    <col min="2" max="2" width="70.28515625" customWidth="1"/>
+    <col min="1" max="1" width="14.19921875" customWidth="1"/>
+    <col min="2" max="2" width="70.3984375" customWidth="1"/>
+    <col min="7" max="7" width="17.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -793,217 +676,261 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:7" hidden="1">
       <c r="B4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" hidden="1">
       <c r="B5" s="4">
         <v>42887</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:7" hidden="1">
       <c r="B6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="B7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="7" spans="1:7" hidden="1">
+      <c r="B7" s="8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" hidden="1">
       <c r="B8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" hidden="1">
       <c r="B9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" hidden="1">
       <c r="B10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" hidden="1">
       <c r="B11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" hidden="1">
+      <c r="G12" s="9"/>
+    </row>
+    <row r="13" spans="1:7" hidden="1">
       <c r="A13" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" hidden="1">
       <c r="B14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" hidden="1">
       <c r="B15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" hidden="1">
       <c r="B16" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" hidden="1">
       <c r="B17" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" hidden="1">
       <c r="B18" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" hidden="1">
       <c r="B19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" hidden="1">
       <c r="B20" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" hidden="1">
       <c r="B21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" hidden="1">
       <c r="B22" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" hidden="1">
       <c r="B23" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" hidden="1">
       <c r="B24" s="5" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" hidden="1"/>
+    <row r="26" spans="1:2" hidden="1"/>
+    <row r="27" spans="1:2" hidden="1"/>
+    <row r="28" spans="1:2" hidden="1"/>
+    <row r="29" spans="1:2" hidden="1"/>
+    <row r="30" spans="1:2" hidden="1">
       <c r="A30" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B30" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" hidden="1">
+      <c r="A31" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B31" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" hidden="1">
+      <c r="B32" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" hidden="1">
+      <c r="B33" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" hidden="1">
+      <c r="B34" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" hidden="1">
+      <c r="B35" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" hidden="1">
+      <c r="B36" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" hidden="1"/>
+    <row r="38" spans="1:2" hidden="1"/>
+    <row r="39" spans="1:2" hidden="1"/>
+    <row r="40" spans="1:2" hidden="1"/>
+    <row r="41" spans="1:2" hidden="1">
+      <c r="A41" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="B41" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" hidden="1">
+      <c r="A42" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="B32" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="B33" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="B34" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="B35" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="B36" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B41" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="5" t="s">
-        <v>24</v>
-      </c>
       <c r="B42" s="7" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" hidden="1">
       <c r="B43" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" hidden="1">
       <c r="B44" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" hidden="1"/>
+    <row r="46" spans="1:2" hidden="1"/>
+    <row r="47" spans="1:2" hidden="1"/>
+    <row r="48" spans="1:2" hidden="1">
       <c r="A48" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" hidden="1">
       <c r="A49" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" hidden="1">
       <c r="B50" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" hidden="1">
       <c r="B51" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" hidden="1">
       <c r="B52" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" hidden="1">
       <c r="B53" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" hidden="1"/>
+    <row r="55" spans="1:2" hidden="1"/>
+    <row r="56" spans="1:2">
+      <c r="B56" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="60">
+      <c r="B57" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="B59" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="B60" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="B61" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B7" r:id="rId1" xr:uid="{0A04DF51-2EA7-644D-8080-450030C60B30}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait" verticalDpi="0" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1013,19 +940,19 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.796875" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="B1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" s="3">
-        <v>1600</v>
+        <v>3600</v>
       </c>
     </row>
   </sheetData>
@@ -1036,49 +963,32 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1086,24 +996,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -1122,70 +1093,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -1287,12 +1211,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cb176f07-3112-4ee9-93fd-ae2cb5f3e433">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="6b15a3a4-8173-42d6-9deb-398ec38eca4b" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{890F7582-7783-415A-B821-0213938B85EB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14F66CB6-ACE6-4BBD-A235-5DFFE8108D75}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <ds:schemaRef ds:uri="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1306,21 +1259,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C230D59-5292-4FC8-BB06-AE7E896CCC36}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{890F7582-7783-415A-B821-0213938B85EB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
+    <ds:schemaRef ds:uri="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <ds:schemaRef ds:uri="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>